--- a/data/merged/2026-10-08/MERGED_ES_Mite-Vacuum_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_ES_Mite-Vacuum_2026-10-08.xlsx
@@ -3443,13 +3443,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3531,13 +3531,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3575,13 +3575,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3619,13 +3619,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4059,13 +4059,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4147,13 +4147,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4279,13 +4279,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4455,13 +4455,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4478,94 +4478,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId33" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Product 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId34" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Product 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId35" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4907,7 +4819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR36"/>
+  <dimension ref="A1:BR34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -7232,45 +7144,45 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B0F2MQCLRJ</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>CREATULIZE</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=CREATULIZE</t>
+          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>CREATULIZE Filtro de Limpieza de vacío para el hogar Accesorios</t>
+          <t>Aspirador de colchón UV-C y ultrasónico doble vaso para cama y sofásAspirador de ácaros inalámbrico para colchones, sofás d</t>
         </is>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0F2MQCLRJ?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GF7CNTYL?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/313+mKfH96L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41CQc-U9WtL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B0F2MQCLRJ</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de mano</t>
+          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de futones</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
@@ -7279,40 +7191,36 @@
         </is>
       </c>
       <c r="O11" s="15">
-        <v>79468</v>
-      </c>
-      <c r="P11" s="15">
-        <v>202623</v>
-      </c>
+        <v>72209</v>
+      </c>
+      <c r="P11" s="15"/>
       <c r="Q11" s="16">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="R11" s="17" t="inlineStr">
         <is>
-          <t>Aspiradoras de mano</t>
+          <t>Aspiradoras de futones</t>
         </is>
       </c>
       <c r="S11" s="18" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T11" s="15">
-        <v>6</v>
-      </c>
-      <c r="U11" s="16">
-        <v>0.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U11" s="16"/>
       <c r="V11" s="15">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="W11" s="15"/>
       <c r="X11" s="15"/>
       <c r="Y11" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z11" s="20">
-        <v>19.99</v>
+        <v>24.99</v>
       </c>
       <c r="AA11"/>
       <c r="AB11"/>
@@ -7320,22 +7228,28 @@
       <c r="AD11" s="19">
         <v>1</v>
       </c>
-      <c r="AE11" s="15">
-        <v>0</v>
-      </c>
+      <c r="AE11" s="15"/>
       <c r="AF11" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG11" s="22">
         <v>0</v>
       </c>
-      <c r="AH11" s="20"/>
+      <c r="AH11" s="20">
+        <v>5.15</v>
+      </c>
       <c r="AI11" s="16">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AJ11"/>
-      <c r="AK11" s="13"/>
-      <c r="AL11" s="19"/>
+      <c r="AK11" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AL11" s="19">
+        <v>149</v>
+      </c>
       <c r="AM11" s="13" t="inlineStr">
         <is>
           <t>FBA</t>
@@ -7345,14 +7259,14 @@
       <c r="AO11" s="13"/>
       <c r="AP11"/>
       <c r="AQ11" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR11" s="19">
         <v>1</v>
       </c>
       <c r="AS11" s="14" t="inlineStr">
         <is>
-          <t>Romiromi</t>
+          <t>liwantech</t>
         </is>
       </c>
       <c r="AT11" s="13" t="inlineStr">
@@ -7367,12 +7281,12 @@
       </c>
       <c r="AV11" s="14" t="inlineStr">
         <is>
-          <t>北京市 北京 100016 CN</t>
+          <t>深圳市 南山区 广东 518000 CN</t>
         </is>
       </c>
       <c r="AW11" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AWR1VM0K04YAS</t>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
         </is>
       </c>
       <c r="AX11" s="13"/>
@@ -7387,19 +7301,47 @@
       <c r="BG11" s="13"/>
       <c r="BH11" s="14"/>
       <c r="BI11" s="23"/>
-      <c r="BJ11" s="23"/>
-      <c r="BK11" s="23"/>
+      <c r="BJ11" s="23" t="inlineStr">
+        <is>
+          <t>1300 Gramos</t>
+        </is>
+      </c>
+      <c r="BK11" s="23" t="inlineStr">
+        <is>
+          <t>1.30 kg</t>
+        </is>
+      </c>
       <c r="BL11" s="23" t="inlineStr">
         <is>
-          <t>16l. x 4an. x 8al. centímetros</t>
+          <t>28l. x 27an. x 11al. centímetros</t>
         </is>
       </c>
       <c r="BM11" s="23"/>
-      <c r="BN11" s="23"/>
-      <c r="BO11" s="23"/>
-      <c r="BP11" s="23"/>
-      <c r="BQ11" s="23"/>
-      <c r="BR11" s="13"/>
+      <c r="BN11" s="23" t="inlineStr">
+        <is>
+          <t>1.3 kg</t>
+        </is>
+      </c>
+      <c r="BO11" s="23" t="inlineStr">
+        <is>
+          <t>1.30 kg</t>
+        </is>
+      </c>
+      <c r="BP11" s="23" t="inlineStr">
+        <is>
+          <t>28 x 27 x 17 cm</t>
+        </is>
+      </c>
+      <c r="BQ11" s="23" t="inlineStr">
+        <is>
+          <t>28.00 x 27.00 x 17.00 cm</t>
+        </is>
+      </c>
+      <c r="BR11" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
@@ -7408,40 +7350,40 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0CJFR8YZ1</t>
         </is>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+          <t>https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0CJFR8YZ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Aspirador de colchón UV-C y ultrasónico doble vaso para cama y sofásAspirador de ácaros inalámbrico para colchones, sofás d</t>
+          <t>JIGOO S300 Pro Aspirador de Ácaros con Sensor de Ácaros y Pantalla Digital, 500W Aspiradora antiácaros con Luz UV, 13KPa de s</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GF7CNTYL?psc=1</t>
+          <t>https://www.amazon.es/dp/B0CJFR8YZ1?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41CQc-U9WtL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71wwrAJ4EpL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0CJFR8YZ1</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
@@ -7455,7 +7397,7 @@
         </is>
       </c>
       <c r="O12" s="15">
-        <v>72209</v>
+        <v>190108</v>
       </c>
       <c r="P12" s="15"/>
       <c r="Q12" s="16">
@@ -7468,89 +7410,89 @@
       </c>
       <c r="S12" s="18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T12" s="15">
-        <v>1</v>
-      </c>
-      <c r="U12" s="16"/>
-      <c r="V12" s="15">
-        <v>25</v>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T12" s="15"/>
+      <c r="U12" s="16">
+        <v>0</v>
+      </c>
+      <c r="V12" s="15"/>
       <c r="W12" s="15"/>
       <c r="X12" s="15"/>
       <c r="Y12" s="19">
         <v>1</v>
       </c>
       <c r="Z12" s="20">
-        <v>24.99</v>
+        <v>72.75</v>
       </c>
       <c r="AA12"/>
       <c r="AB12"/>
       <c r="AC12" s="2"/>
       <c r="AD12" s="19">
+        <v>687</v>
+      </c>
+      <c r="AE12" s="15">
         <v>1</v>
       </c>
-      <c r="AE12" s="15"/>
       <c r="AF12" s="21">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AG12" s="22">
         <v>0</v>
       </c>
       <c r="AH12" s="20">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="AI12" s="16">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="AJ12"/>
       <c r="AK12" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AL12" s="19">
-        <v>149</v>
+        <v>1111</v>
       </c>
       <c r="AM12" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN12" s="13"/>
       <c r="AO12" s="13"/>
       <c r="AP12"/>
       <c r="AQ12" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AR12" s="19">
         <v>1</v>
       </c>
       <c r="AS12" s="14" t="inlineStr">
         <is>
-          <t>liwantech</t>
+          <t>GOOD PRICE ONLY</t>
         </is>
       </c>
       <c r="AT12" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU12" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="AV12" s="14" t="inlineStr">
         <is>
-          <t>深圳市 南山区 广东 518000 CN</t>
+          <t>Jud. Neamt 617218 RO</t>
         </is>
       </c>
       <c r="AW12" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SBFZKR4LHBTM</t>
         </is>
       </c>
       <c r="AX12" s="13"/>
@@ -7558,8 +7500,16 @@
       <c r="AZ12" s="13"/>
       <c r="BA12" s="13"/>
       <c r="BB12" s="13"/>
-      <c r="BC12" s="13"/>
-      <c r="BD12" s="13"/>
+      <c r="BC12" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD12" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE12" s="13"/>
       <c r="BF12" s="13"/>
       <c r="BG12" s="13"/>
@@ -7567,38 +7517,42 @@
       <c r="BI12" s="23"/>
       <c r="BJ12" s="23" t="inlineStr">
         <is>
-          <t>1300 Gramos</t>
+          <t>2.3 kg</t>
         </is>
       </c>
       <c r="BK12" s="23" t="inlineStr">
         <is>
-          <t>1.30 kg</t>
+          <t>2.30 kg</t>
         </is>
       </c>
       <c r="BL12" s="23" t="inlineStr">
         <is>
-          <t>28l. x 27an. x 11al. centímetros</t>
-        </is>
-      </c>
-      <c r="BM12" s="23"/>
+          <t>30.5 x 20.3 x 38.1 cm</t>
+        </is>
+      </c>
+      <c r="BM12" s="23" t="inlineStr">
+        <is>
+          <t>30.50 x 20.30 x 38.10 cm</t>
+        </is>
+      </c>
       <c r="BN12" s="23" t="inlineStr">
         <is>
-          <t>1.3 kg</t>
+          <t>2.76 kg</t>
         </is>
       </c>
       <c r="BO12" s="23" t="inlineStr">
         <is>
-          <t>1.30 kg</t>
+          <t>2.76 kg</t>
         </is>
       </c>
       <c r="BP12" s="23" t="inlineStr">
         <is>
-          <t>28 x 27 x 17 cm</t>
+          <t>36.2 x 31.3 x 24.7 cm</t>
         </is>
       </c>
       <c r="BQ12" s="23" t="inlineStr">
         <is>
-          <t>28.00 x 27.00 x 17.00 cm</t>
+          <t>36.20 x 31.30 x 24.70 cm</t>
         </is>
       </c>
       <c r="BR12" s="13" t="inlineStr">
@@ -7614,216 +7568,104 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0CJFR8YZ1</t>
+          <t>B0D83SRY9V</t>
         </is>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>JIGOO</t>
-        </is>
-      </c>
+      <c r="F13" s="14"/>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0CJFR8YZ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.esundefined</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>JIGOO S300 Pro Aspirador de Ácaros con Sensor de Ácaros y Pantalla Digital, 500W Aspiradora antiácaros con Luz UV, 13KPa de s</t>
+          <t>Aspiradora Antiacaros, 16Kpa Aspiradora Antiácaros con Luz UV, Elimina el 99,9% de los Alérgenos, para Colchones, Camas, Sofá</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0CJFR8YZ1?psc=1</t>
+          <t>https://www.amazon.es/dp/B0D83SRY9V?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71wwrAJ4EpL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51LjSaAmb9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0CJFR8YZ1</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de futones</t>
-        </is>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O13" s="15">
-        <v>190108</v>
-      </c>
+          <t>B0D83SRY9V</t>
+        </is>
+      </c>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="15"/>
       <c r="P13" s="15"/>
-      <c r="Q13" s="16">
-        <v>0</v>
-      </c>
-      <c r="R13" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras de futones</t>
-        </is>
-      </c>
-      <c r="S13" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="18"/>
       <c r="T13" s="15"/>
-      <c r="U13" s="16">
-        <v>0</v>
-      </c>
+      <c r="U13" s="16"/>
       <c r="V13" s="15"/>
       <c r="W13" s="15"/>
       <c r="X13" s="15"/>
-      <c r="Y13" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="20">
-        <v>72.75</v>
-      </c>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="20"/>
       <c r="AA13"/>
       <c r="AB13"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="19">
-        <v>687</v>
-      </c>
-      <c r="AE13" s="15">
-        <v>1</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="AE13" s="15"/>
       <c r="AF13" s="21">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AG13" s="22">
         <v>0</v>
       </c>
-      <c r="AH13" s="20">
-        <v>5.8</v>
-      </c>
+      <c r="AH13" s="20"/>
       <c r="AI13" s="16">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="AJ13"/>
-      <c r="AK13" s="13" t="inlineStr">
-        <is>
-          <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AL13" s="19">
-        <v>1111</v>
-      </c>
-      <c r="AM13" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK13" s="13"/>
+      <c r="AL13" s="19"/>
+      <c r="AM13" s="13"/>
       <c r="AN13" s="13"/>
       <c r="AO13" s="13"/>
       <c r="AP13"/>
-      <c r="AQ13" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR13" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS13" s="14" t="inlineStr">
-        <is>
-          <t>GOOD PRICE ONLY</t>
-        </is>
-      </c>
-      <c r="AT13" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU13" s="13" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="AV13" s="14" t="inlineStr">
-        <is>
-          <t>Jud. Neamt 617218 RO</t>
-        </is>
-      </c>
-      <c r="AW13" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SBFZKR4LHBTM</t>
-        </is>
-      </c>
+      <c r="AQ13" s="19"/>
+      <c r="AR13" s="19"/>
+      <c r="AS13" s="14"/>
+      <c r="AT13" s="13"/>
+      <c r="AU13" s="13"/>
+      <c r="AV13" s="14"/>
+      <c r="AW13" s="13"/>
       <c r="AX13" s="13"/>
       <c r="AY13" s="13"/>
       <c r="AZ13" s="13"/>
       <c r="BA13" s="13"/>
       <c r="BB13" s="13"/>
-      <c r="BC13" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD13" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC13" s="13"/>
+      <c r="BD13" s="13"/>
       <c r="BE13" s="13"/>
       <c r="BF13" s="13"/>
       <c r="BG13" s="13"/>
       <c r="BH13" s="14"/>
       <c r="BI13" s="23"/>
-      <c r="BJ13" s="23" t="inlineStr">
-        <is>
-          <t>2.3 kg</t>
-        </is>
-      </c>
-      <c r="BK13" s="23" t="inlineStr">
-        <is>
-          <t>2.30 kg</t>
-        </is>
-      </c>
-      <c r="BL13" s="23" t="inlineStr">
-        <is>
-          <t>30.5 x 20.3 x 38.1 cm</t>
-        </is>
-      </c>
-      <c r="BM13" s="23" t="inlineStr">
-        <is>
-          <t>30.50 x 20.30 x 38.10 cm</t>
-        </is>
-      </c>
-      <c r="BN13" s="23" t="inlineStr">
-        <is>
-          <t>2.76 kg</t>
-        </is>
-      </c>
-      <c r="BO13" s="23" t="inlineStr">
-        <is>
-          <t>2.76 kg</t>
-        </is>
-      </c>
-      <c r="BP13" s="23" t="inlineStr">
-        <is>
-          <t>36.2 x 31.3 x 24.7 cm</t>
-        </is>
-      </c>
-      <c r="BQ13" s="23" t="inlineStr">
-        <is>
-          <t>36.20 x 31.30 x 24.70 cm</t>
-        </is>
-      </c>
-      <c r="BR13" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BJ13" s="23"/>
+      <c r="BK13" s="23"/>
+      <c r="BL13" s="23"/>
+      <c r="BM13" s="23"/>
+      <c r="BN13" s="23"/>
+      <c r="BO13" s="23"/>
+      <c r="BP13" s="23"/>
+      <c r="BQ13" s="23"/>
+      <c r="BR13" s="13"/>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
@@ -7832,104 +7674,212 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0D83SRY9V</t>
+          <t>B0D9BQHSWQ</t>
         </is>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Jimmy</t>
+        </is>
+      </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.esundefined</t>
+          <t>https://www.amazon.es/Jimmy/b/ref=bl_dp_s_web_17484947031?ie=UTF8&amp;node=17484947031&amp;field-lbr_brands_browse-bin=Jimmy</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Aspiradora Antiacaros, 16Kpa Aspiradora Antiácaros con Luz UV, Elimina el 99,9% de los Alérgenos, para Colchones, Camas, Sofá</t>
+          <t>Jimmy BX6 Lite Aspirador Antiácaros para Colchones, con Potencia de Succión de 600 W, 15 kpa, Aspiradora con Sensor de Polvo,</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0D83SRY9V?psc=1</t>
+          <t>https://www.amazon.es/dp/B0D9BQHSWQ?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51LjSaAmb9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41BwZxWS8oL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0D83SRY9V</t>
-        </is>
-      </c>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="18"/>
+          <t>B0D9BQHSWQ</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de futones</t>
+        </is>
+      </c>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t>Hogar y cocina</t>
+        </is>
+      </c>
+      <c r="O14" s="15">
+        <v>70491</v>
+      </c>
+      <c r="P14" s="15">
+        <v>12285</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="R14" s="17" t="inlineStr">
+        <is>
+          <t>Aspiradoras de futones</t>
+        </is>
+      </c>
+      <c r="S14" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="T14" s="15"/>
       <c r="U14" s="16"/>
       <c r="V14" s="15"/>
       <c r="W14" s="15"/>
       <c r="X14" s="15"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="20"/>
+      <c r="Y14" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="20">
+        <v>119.99</v>
+      </c>
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14" s="2"/>
       <c r="AD14" s="19">
-        <v>27</v>
-      </c>
-      <c r="AE14" s="15"/>
+        <v>138</v>
+      </c>
+      <c r="AE14" s="15">
+        <v>2</v>
+      </c>
       <c r="AF14" s="21">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AG14" s="22">
         <v>0</v>
       </c>
-      <c r="AH14" s="20"/>
+      <c r="AH14" s="20">
+        <v>6.05</v>
+      </c>
       <c r="AI14" s="16">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AJ14"/>
-      <c r="AK14" s="13"/>
-      <c r="AL14" s="19"/>
-      <c r="AM14" s="13"/>
+      <c r="AK14" s="13" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AL14" s="19">
+        <v>727</v>
+      </c>
+      <c r="AM14" s="13" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
       <c r="AN14" s="13"/>
       <c r="AO14" s="13"/>
       <c r="AP14"/>
-      <c r="AQ14" s="19"/>
-      <c r="AR14" s="19"/>
-      <c r="AS14" s="14"/>
-      <c r="AT14" s="13"/>
-      <c r="AU14" s="13"/>
-      <c r="AV14" s="14"/>
-      <c r="AW14" s="13"/>
+      <c r="AQ14" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR14" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS14" s="14" t="inlineStr">
+        <is>
+          <t>NEXO HOME</t>
+        </is>
+      </c>
+      <c r="AT14" s="13" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU14" s="13" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AV14" s="14" t="inlineStr">
+        <is>
+          <t>Barcelona Barcelona 08013 ES</t>
+        </is>
+      </c>
+      <c r="AW14" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UUYGTGLOQBB0</t>
+        </is>
+      </c>
       <c r="AX14" s="13"/>
       <c r="AY14" s="13"/>
       <c r="AZ14" s="13"/>
       <c r="BA14" s="13"/>
       <c r="BB14" s="13"/>
-      <c r="BC14" s="13"/>
-      <c r="BD14" s="13"/>
+      <c r="BC14" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD14" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE14" s="13"/>
       <c r="BF14" s="13"/>
       <c r="BG14" s="13"/>
       <c r="BH14" s="14"/>
       <c r="BI14" s="23"/>
-      <c r="BJ14" s="23"/>
-      <c r="BK14" s="23"/>
-      <c r="BL14" s="23"/>
+      <c r="BJ14" s="23" t="inlineStr">
+        <is>
+          <t>1,9 Kilogramos</t>
+        </is>
+      </c>
+      <c r="BK14" s="23" t="inlineStr">
+        <is>
+          <t>1.90 kg</t>
+        </is>
+      </c>
+      <c r="BL14" s="23" t="inlineStr">
+        <is>
+          <t>30,5l. x 20an. x 38,5al. centímetros</t>
+        </is>
+      </c>
       <c r="BM14" s="23"/>
-      <c r="BN14" s="23"/>
-      <c r="BO14" s="23"/>
-      <c r="BP14" s="23"/>
-      <c r="BQ14" s="23"/>
-      <c r="BR14" s="13"/>
+      <c r="BN14" s="23" t="inlineStr">
+        <is>
+          <t>2.89 kg</t>
+        </is>
+      </c>
+      <c r="BO14" s="23" t="inlineStr">
+        <is>
+          <t>2.89 kg</t>
+        </is>
+      </c>
+      <c r="BP14" s="23" t="inlineStr">
+        <is>
+          <t>38.7 x 31.5 x 20.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ14" s="23" t="inlineStr">
+        <is>
+          <t>38.70 x 31.50 x 20.20 cm</t>
+        </is>
+      </c>
+      <c r="BR14" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
@@ -7938,212 +7888,104 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0D9BQHSWQ</t>
+          <t>B0DNYVJ4PL</t>
         </is>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>Jimmy</t>
-        </is>
-      </c>
+      <c r="F15" s="14"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/Jimmy/b/ref=bl_dp_s_web_17484947031?ie=UTF8&amp;node=17484947031&amp;field-lbr_brands_browse-bin=Jimmy</t>
+          <t>https://www.amazon.esundefined</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Jimmy BX6 Lite Aspirador Antiácaros para Colchones, con Potencia de Succión de 600 W, 15 kpa, Aspiradora con Sensor de Polvo,</t>
+          <t>FEPPO Aspirador de ácaros para colchones, 16 kpa con luz UV-C de 253,7 nm, calor 140 °F, filtro HEPA y ultrasonidos, aspirado</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0D9BQHSWQ?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DNYVJ4PL?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41BwZxWS8oL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71X5KPbPpoL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0D9BQHSWQ</t>
-        </is>
-      </c>
-      <c r="M15" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de futones</t>
-        </is>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O15" s="15">
-        <v>70491</v>
-      </c>
-      <c r="P15" s="15">
-        <v>12285</v>
-      </c>
-      <c r="Q15" s="16">
-        <v>0.05</v>
-      </c>
-      <c r="R15" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras de futones</t>
-        </is>
-      </c>
-      <c r="S15" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>B0DNYVJ4PL</t>
+        </is>
+      </c>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="18"/>
       <c r="T15" s="15"/>
       <c r="U15" s="16"/>
       <c r="V15" s="15"/>
       <c r="W15" s="15"/>
       <c r="X15" s="15"/>
-      <c r="Y15" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="20">
-        <v>119.99</v>
-      </c>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="20"/>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15" s="2"/>
       <c r="AD15" s="19">
-        <v>138</v>
-      </c>
-      <c r="AE15" s="15">
-        <v>2</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="AE15" s="15"/>
       <c r="AF15" s="21">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AG15" s="22">
         <v>0</v>
       </c>
-      <c r="AH15" s="20">
-        <v>6.05</v>
-      </c>
+      <c r="AH15" s="20"/>
       <c r="AI15" s="16">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ15"/>
-      <c r="AK15" s="13" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AL15" s="19">
-        <v>727</v>
-      </c>
-      <c r="AM15" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK15" s="13"/>
+      <c r="AL15" s="19"/>
+      <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
       <c r="AO15" s="13"/>
       <c r="AP15"/>
-      <c r="AQ15" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR15" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS15" s="14" t="inlineStr">
-        <is>
-          <t>NEXO HOME</t>
-        </is>
-      </c>
-      <c r="AT15" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU15" s="13" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AV15" s="14" t="inlineStr">
-        <is>
-          <t>Barcelona Barcelona 08013 ES</t>
-        </is>
-      </c>
-      <c r="AW15" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UUYGTGLOQBB0</t>
-        </is>
-      </c>
+      <c r="AQ15" s="19"/>
+      <c r="AR15" s="19"/>
+      <c r="AS15" s="14"/>
+      <c r="AT15" s="13"/>
+      <c r="AU15" s="13"/>
+      <c r="AV15" s="14"/>
+      <c r="AW15" s="13"/>
       <c r="AX15" s="13"/>
       <c r="AY15" s="13"/>
       <c r="AZ15" s="13"/>
       <c r="BA15" s="13"/>
       <c r="BB15" s="13"/>
-      <c r="BC15" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD15" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC15" s="13"/>
+      <c r="BD15" s="13"/>
       <c r="BE15" s="13"/>
       <c r="BF15" s="13"/>
       <c r="BG15" s="13"/>
       <c r="BH15" s="14"/>
       <c r="BI15" s="23"/>
-      <c r="BJ15" s="23" t="inlineStr">
-        <is>
-          <t>1,9 Kilogramos</t>
-        </is>
-      </c>
-      <c r="BK15" s="23" t="inlineStr">
-        <is>
-          <t>1.90 kg</t>
-        </is>
-      </c>
-      <c r="BL15" s="23" t="inlineStr">
-        <is>
-          <t>30,5l. x 20an. x 38,5al. centímetros</t>
-        </is>
-      </c>
+      <c r="BJ15" s="23"/>
+      <c r="BK15" s="23"/>
+      <c r="BL15" s="23"/>
       <c r="BM15" s="23"/>
-      <c r="BN15" s="23" t="inlineStr">
-        <is>
-          <t>2.89 kg</t>
-        </is>
-      </c>
-      <c r="BO15" s="23" t="inlineStr">
-        <is>
-          <t>2.89 kg</t>
-        </is>
-      </c>
-      <c r="BP15" s="23" t="inlineStr">
-        <is>
-          <t>38.7 x 31.5 x 20.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ15" s="23" t="inlineStr">
-        <is>
-          <t>38.70 x 31.50 x 20.20 cm</t>
-        </is>
-      </c>
-      <c r="BR15" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BN15" s="23"/>
+      <c r="BO15" s="23"/>
+      <c r="BP15" s="23"/>
+      <c r="BQ15" s="23"/>
+      <c r="BR15" s="13"/>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
@@ -8152,7 +7994,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0DNYVJ4PL</t>
+          <t>B0DNZ5LDQX</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -8165,23 +8007,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>FEPPO Aspirador de ácaros para colchones, 16 kpa con luz UV-C de 253,7 nm, calor 140 °F, filtro HEPA y ultrasonidos, aspirado</t>
+          <t>Liwankaqi Aspirador de ácaros 14 kPa, velocidad de esterilización con lámparas UV LED, aspirador de colchón con detergente y</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DNYVJ4PL?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DNZ5LDQX?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71X5KPbPpoL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61YjHSHoT6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0DNYVJ4PL</t>
+          <t>B0DNZ5LDQX</t>
         </is>
       </c>
       <c r="M16" s="14"/>
@@ -8202,11 +8044,11 @@
       <c r="AB16"/>
       <c r="AC16" s="2"/>
       <c r="AD16" s="19">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="AE16" s="15"/>
       <c r="AF16" s="21">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AG16" s="22">
         <v>0</v>
@@ -8258,7 +8100,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0DNZ5LDQX</t>
+          <t>B0DT1D15C6</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -8271,23 +8113,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspirador de ácaros 14 kPa, velocidad de esterilización con lámparas UV LED, aspirador de colchón con detergente y</t>
+          <t>CREATULIZE Robot X1, Aspirador de Acaros, Navegación Inteligente, Limpieza Automática de Cama, Manos Libres, Detección de Bor</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DNZ5LDQX?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DT1D15C6?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61YjHSHoT6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81vdWh-NSLL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0DNZ5LDQX</t>
+          <t>B0DT1D15C6</t>
         </is>
       </c>
       <c r="M17" s="14"/>
@@ -8308,11 +8150,11 @@
       <c r="AB17"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="19">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AE17" s="15"/>
       <c r="AF17" s="21">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AG17" s="22">
         <v>0</v>
@@ -8364,7 +8206,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0DT1D15C6</t>
+          <t>B0DWK8LJF9</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -8377,23 +8219,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>CREATULIZE Robot X1, Aspirador de Acaros, Navegación Inteligente, Limpieza Automática de Cama, Manos Libres, Detección de Bor</t>
+          <t>aichilra Aspirador de ácaros para colchones, 100 W, portátil, inalámbrico, con doble aspiradora y UV-C y ultrasonido para la</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DT1D15C6?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DWK8LJF9?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81vdWh-NSLL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61TZ0rMGBrL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0DT1D15C6</t>
+          <t>B0DWK8LJF9</t>
         </is>
       </c>
       <c r="M18" s="14"/>
@@ -8414,7 +8256,7 @@
       <c r="AB18"/>
       <c r="AC18" s="2"/>
       <c r="AD18" s="19">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="AE18" s="15"/>
       <c r="AF18" s="21">
@@ -8470,7 +8312,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0DWK8LJF9</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -8483,23 +8325,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>aichilra Aspirador de ácaros para colchones, 100 W, portátil, inalámbrico, con doble aspiradora y UV-C y ultrasonido para la</t>
+          <t>Aspiradora Antiacaros, Luz UV-C y 400WsElimina el 99,9%| Aire Caliente a 60 Grados Centígrados, Alergenos y Pelos de Mascota</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DWK8LJF9?psc=1</t>
+          <t>https://www.amazon.es/dp/B0F6XNKG8M?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61TZ0rMGBrL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0DWK8LJF9</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="M19" s="14"/>
@@ -8520,11 +8362,11 @@
       <c r="AB19"/>
       <c r="AC19" s="2"/>
       <c r="AD19" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE19" s="15"/>
       <c r="AF19" s="21">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AG19" s="22">
         <v>0</v>
@@ -8576,7 +8418,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F8HD3649</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -8589,23 +8431,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Aspiradora Antiacaros, Luz UV-C y 400WsElimina el 99,9%| Aire Caliente a 60 Grados Centígrados, Alergenos y Pelos de Mascota</t>
+          <t>Aspiradora Antiacaros con Luz UV, 16 Kpa</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0F6XNKG8M?psc=1</t>
+          <t>https://www.amazon.es/dp/B0F8HD3649?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F8HD3649</t>
         </is>
       </c>
       <c r="M20" s="14"/>
@@ -8626,11 +8468,11 @@
       <c r="AB20"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="19">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="AE20" s="15"/>
       <c r="AF20" s="21">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AG20" s="22">
         <v>0</v>
@@ -8682,7 +8524,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0F8HD3649</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -8695,23 +8537,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Aspiradora Antiacaros con Luz UV, 16 Kpa</t>
+          <t>Liwankaqi Aspiradora antiácaros UV-C y ultrasonidos, 8 KPa, antialérgenos para cama, sofás, alfombras</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0F8HD3649?psc=1</t>
+          <t>https://www.amazon.es/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0F8HD3649</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="M21" s="14"/>
@@ -8732,11 +8574,11 @@
       <c r="AB21"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="19">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="AE21" s="15"/>
       <c r="AF21" s="21">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" s="22">
         <v>0</v>
@@ -8788,83 +8630,143 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FBGQY9YP</t>
         </is>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Fey</t>
+        </is>
+      </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.esundefined</t>
+          <t>https://www.amazon.es/stores/Fey/page/43F7FFA5-3E54-4A0B-BF57-3795C4422856?lp_asin=B0FBGQY9YP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspiradora antiácaros UV-C y ultrasonidos, 8 KPa, antialérgenos para cama, sofás, alfombras</t>
+          <t>Fey Aspirador antiácaros para colchones de 16 KPA, potente limpiador de colchones con luz UV-C, sensor de ácaros del polvo, f</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FBGQY9YP?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
-        </is>
-      </c>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="15"/>
+          <t>B0FBGQY9YP</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
+          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de futones</t>
+        </is>
+      </c>
+      <c r="N22" s="14" t="inlineStr">
+        <is>
+          <t>Hogar y cocina</t>
+        </is>
+      </c>
+      <c r="O22" s="15">
+        <v>414664</v>
+      </c>
       <c r="P22" s="15"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="18"/>
+      <c r="Q22" s="16">
+        <v>0</v>
+      </c>
+      <c r="R22" s="17" t="inlineStr">
+        <is>
+          <t>Aspiradoras de futones</t>
+        </is>
+      </c>
+      <c r="S22" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="T22" s="15"/>
       <c r="U22" s="16"/>
       <c r="V22" s="15"/>
       <c r="W22" s="15"/>
       <c r="X22" s="15"/>
-      <c r="Y22" s="19"/>
-      <c r="Z22" s="20"/>
+      <c r="Y22" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="20">
+        <v>59.99</v>
+      </c>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE22" s="15"/>
       <c r="AF22" s="21">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
       </c>
       <c r="AH22" s="20"/>
       <c r="AI22" s="16">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AJ22"/>
-      <c r="AK22" s="13"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="13"/>
+      <c r="AK22" s="13" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AL22" s="19">
+        <v>237</v>
+      </c>
+      <c r="AM22" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN22" s="13"/>
       <c r="AO22" s="13"/>
       <c r="AP22"/>
       <c r="AQ22" s="19"/>
-      <c r="AR22" s="19"/>
-      <c r="AS22" s="14"/>
-      <c r="AT22" s="13"/>
-      <c r="AU22" s="13"/>
-      <c r="AV22" s="14"/>
-      <c r="AW22" s="13"/>
+      <c r="AR22" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS22" s="14" t="inlineStr">
+        <is>
+          <t>Jierun-EU</t>
+        </is>
+      </c>
+      <c r="AT22" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU22" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV22" s="14" t="inlineStr">
+        <is>
+          <t>扬州市 江苏 225002 CN</t>
+        </is>
+      </c>
+      <c r="AW22" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3MSJ66TMU8M67</t>
+        </is>
+      </c>
       <c r="AX22" s="13"/>
       <c r="AY22" s="13"/>
       <c r="AZ22" s="13"/>
@@ -8879,8 +8781,16 @@
       <c r="BI22" s="23"/>
       <c r="BJ22" s="23"/>
       <c r="BK22" s="23"/>
-      <c r="BL22" s="23"/>
-      <c r="BM22" s="23"/>
+      <c r="BL22" s="23" t="inlineStr">
+        <is>
+          <t>29 x 24 x 23.5 cm</t>
+        </is>
+      </c>
+      <c r="BM22" s="23" t="inlineStr">
+        <is>
+          <t>29.00 x 24.00 x 23.50 cm</t>
+        </is>
+      </c>
       <c r="BN22" s="23"/>
       <c r="BO22" s="23"/>
       <c r="BP22" s="23"/>
@@ -8894,143 +8804,83 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0FBGQY9YP</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>Fey</t>
-        </is>
-      </c>
+      <c r="F23" s="14"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Fey/page/43F7FFA5-3E54-4A0B-BF57-3795C4422856?lp_asin=B0FBGQY9YP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.esundefined</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Fey Aspirador antiácaros para colchones de 16 KPA, potente limpiador de colchones con luz UV-C, sensor de ácaros del polvo, f</t>
+          <t>JIGOO T600 T600 - Tetina antiácaros/Floral Delight (aceite esencial de plantas)</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FBGQY9YP?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FDWVV95V?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0FBGQY9YP</t>
-        </is>
-      </c>
-      <c r="M23" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de futones</t>
-        </is>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O23" s="15">
-        <v>414664</v>
-      </c>
+          <t>B0FDWVV95V</t>
+        </is>
+      </c>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="15"/>
       <c r="P23" s="15"/>
-      <c r="Q23" s="16">
-        <v>0</v>
-      </c>
-      <c r="R23" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras de futones</t>
-        </is>
-      </c>
-      <c r="S23" s="18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="18"/>
       <c r="T23" s="15"/>
       <c r="U23" s="16"/>
       <c r="V23" s="15"/>
       <c r="W23" s="15"/>
       <c r="X23" s="15"/>
-      <c r="Y23" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="20">
-        <v>59.99</v>
-      </c>
+      <c r="Y23" s="19"/>
+      <c r="Z23" s="20"/>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="19">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AE23" s="15"/>
       <c r="AF23" s="21">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
       </c>
       <c r="AH23" s="20"/>
       <c r="AI23" s="16">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AJ23"/>
-      <c r="AK23" s="13" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AL23" s="19">
-        <v>237</v>
-      </c>
-      <c r="AM23" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK23" s="13"/>
+      <c r="AL23" s="19"/>
+      <c r="AM23" s="13"/>
       <c r="AN23" s="13"/>
       <c r="AO23" s="13"/>
       <c r="AP23"/>
       <c r="AQ23" s="19"/>
-      <c r="AR23" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS23" s="14" t="inlineStr">
-        <is>
-          <t>Jierun-EU</t>
-        </is>
-      </c>
-      <c r="AT23" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU23" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV23" s="14" t="inlineStr">
-        <is>
-          <t>扬州市 江苏 225002 CN</t>
-        </is>
-      </c>
-      <c r="AW23" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3MSJ66TMU8M67</t>
-        </is>
-      </c>
+      <c r="AR23" s="19"/>
+      <c r="AS23" s="14"/>
+      <c r="AT23" s="13"/>
+      <c r="AU23" s="13"/>
+      <c r="AV23" s="14"/>
+      <c r="AW23" s="13"/>
       <c r="AX23" s="13"/>
       <c r="AY23" s="13"/>
       <c r="AZ23" s="13"/>
@@ -9045,16 +8895,8 @@
       <c r="BI23" s="23"/>
       <c r="BJ23" s="23"/>
       <c r="BK23" s="23"/>
-      <c r="BL23" s="23" t="inlineStr">
-        <is>
-          <t>29 x 24 x 23.5 cm</t>
-        </is>
-      </c>
-      <c r="BM23" s="23" t="inlineStr">
-        <is>
-          <t>29.00 x 24.00 x 23.50 cm</t>
-        </is>
-      </c>
+      <c r="BL23" s="23"/>
+      <c r="BM23" s="23"/>
       <c r="BN23" s="23"/>
       <c r="BO23" s="23"/>
       <c r="BP23" s="23"/>
@@ -9068,206 +8910,104 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0FBX24WH6</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>syayw</t>
-        </is>
-      </c>
+      <c r="F24" s="14"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=syayw</t>
+          <t>https://www.amazon.esundefined</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>syayw Limpiador Varuum – 68 W Fuerte Cama vacío para Limpieza ProfundasEliminador de para Mascotas vacío para Cojines de so</t>
+          <t>Yaasier Aspirador de Ácaros, Mini Aspirador Antiácaros para Colchones con Luz UV, Aspiradora de Mano con Filtro HEPA para Col</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FBX24WH6?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FKRC3KQY?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61LvanTuKlL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0FBX24WH6</t>
-        </is>
-      </c>
-      <c r="M24" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de mano</t>
-        </is>
-      </c>
-      <c r="N24" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O24" s="15">
-        <v>1528039</v>
-      </c>
+          <t>B0FKRC3KQY</t>
+        </is>
+      </c>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="15"/>
       <c r="P24" s="15"/>
-      <c r="Q24" s="16">
-        <v>0</v>
-      </c>
-      <c r="R24" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras de futones
-Aspiradoras de mano</t>
-        </is>
-      </c>
-      <c r="S24" s="18" t="inlineStr">
-        <is>
-          <t>25
-1817</t>
-        </is>
-      </c>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="18"/>
       <c r="T24" s="15"/>
       <c r="U24" s="16"/>
       <c r="V24" s="15"/>
       <c r="W24" s="15"/>
       <c r="X24" s="15"/>
-      <c r="Y24" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="20">
-        <v>38.11</v>
-      </c>
+      <c r="Y24" s="19"/>
+      <c r="Z24" s="20"/>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24" s="2"/>
-      <c r="AD24" s="19"/>
+      <c r="AD24" s="19">
+        <v>15</v>
+      </c>
       <c r="AE24" s="15"/>
-      <c r="AF24" s="21"/>
+      <c r="AF24" s="21">
+        <v>3.3</v>
+      </c>
       <c r="AG24" s="22">
         <v>0</v>
       </c>
-      <c r="AH24" s="20">
-        <v>5.05</v>
-      </c>
+      <c r="AH24" s="20"/>
       <c r="AI24" s="16">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AJ24"/>
-      <c r="AK24" s="13" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AL24" s="19">
-        <v>309</v>
-      </c>
-      <c r="AM24" s="13" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
+      <c r="AK24" s="13"/>
+      <c r="AL24" s="19"/>
+      <c r="AM24" s="13"/>
       <c r="AN24" s="13"/>
       <c r="AO24" s="13"/>
       <c r="AP24"/>
-      <c r="AQ24" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR24" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS24" s="14" t="inlineStr">
-        <is>
-          <t>nousaeg</t>
-        </is>
-      </c>
-      <c r="AT24" s="13" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU24" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV24" s="14" t="inlineStr">
-        <is>
-          <t>蚌埠市 蚌山区 安徽 233000 CN</t>
-        </is>
-      </c>
-      <c r="AW24" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3T9BSXCSWI46M</t>
-        </is>
-      </c>
+      <c r="AQ24" s="19"/>
+      <c r="AR24" s="19"/>
+      <c r="AS24" s="14"/>
+      <c r="AT24" s="13"/>
+      <c r="AU24" s="13"/>
+      <c r="AV24" s="14"/>
+      <c r="AW24" s="13"/>
       <c r="AX24" s="13"/>
       <c r="AY24" s="13"/>
       <c r="AZ24" s="13"/>
       <c r="BA24" s="13"/>
       <c r="BB24" s="13"/>
-      <c r="BC24" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC24" s="13"/>
       <c r="BD24" s="13"/>
       <c r="BE24" s="13"/>
       <c r="BF24" s="13"/>
       <c r="BG24" s="13"/>
       <c r="BH24" s="14"/>
       <c r="BI24" s="23"/>
-      <c r="BJ24" s="23" t="inlineStr">
-        <is>
-          <t>1,02 kg</t>
-        </is>
-      </c>
-      <c r="BK24" s="23" t="inlineStr">
-        <is>
-          <t>1.02 kg</t>
-        </is>
-      </c>
-      <c r="BL24" s="23" t="inlineStr">
-        <is>
-          <t>26.9 x 25.2 x 14.3 cm</t>
-        </is>
-      </c>
-      <c r="BM24" s="23" t="inlineStr">
-        <is>
-          <t>26.90 x 25.20 x 14.30 cm</t>
-        </is>
-      </c>
-      <c r="BN24" s="23" t="inlineStr">
-        <is>
-          <t>1.02 kg</t>
-        </is>
-      </c>
-      <c r="BO24" s="23" t="inlineStr">
-        <is>
-          <t>1.02 kg</t>
-        </is>
-      </c>
-      <c r="BP24" s="23" t="inlineStr">
-        <is>
-          <t>26.9 x 25.2 x 14.3 cm</t>
-        </is>
-      </c>
-      <c r="BQ24" s="23" t="inlineStr">
-        <is>
-          <t>26.90 x 25.20 x 14.30 cm</t>
-        </is>
-      </c>
-      <c r="BR24" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BJ24" s="23"/>
+      <c r="BK24" s="23"/>
+      <c r="BL24" s="23"/>
+      <c r="BM24" s="23"/>
+      <c r="BN24" s="23"/>
+      <c r="BO24" s="23"/>
+      <c r="BP24" s="23"/>
+      <c r="BQ24" s="23"/>
+      <c r="BR24" s="13"/>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
@@ -9276,7 +9016,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FLXSG7JN</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -9289,23 +9029,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 T600 - Tetina antiácaros/Floral Delight (aceite esencial de plantas)</t>
+          <t>ENCHE Limpiador de ácaros con luz UV contra chinches – Limpiador de tapicería elimina el 99,9% de bacterias, alérgenos y ácar</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FLXSG7JN?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FLXSG7JN</t>
         </is>
       </c>
       <c r="M25" s="14"/>
@@ -9326,11 +9066,11 @@
       <c r="AB25"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="19">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE25" s="15"/>
       <c r="AF25" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -9382,7 +9122,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -9395,23 +9135,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirador de Ácaros, Mini Aspirador Antiácaros para Colchones con Luz UV, Aspiradora de Mano con Filtro HEPA para Col</t>
+          <t>Mayking Teant Aspiradora para Colchones 2 Velocidades (14 kPa/18 kPa)</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FKRC3KQY?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FN3GPQZM?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="M26" s="14"/>
@@ -9432,11 +9172,11 @@
       <c r="AB26"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="19">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="AE26" s="15"/>
       <c r="AF26" s="21">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
@@ -9488,7 +9228,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FLXSG7JN</t>
+          <t>B0FVS559GZ</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -9501,23 +9241,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>ENCHE Limpiador de ácaros con luz UV contra chinches – Limpiador de tapicería elimina el 99,9% de bacterias, alérgenos y ácar</t>
+          <t>Yaasier Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanent</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FLXSG7JN?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FVS559GZ?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0FLXSG7JN</t>
+          <t>B0FVS559GZ</t>
         </is>
       </c>
       <c r="M27" s="14"/>
@@ -9538,11 +9278,11 @@
       <c r="AB27"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="AE27" s="15"/>
       <c r="AF27" s="21">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -9594,7 +9334,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9607,23 +9347,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Mayking Teant Aspiradora para Colchones 2 Velocidades (14 kPa/18 kPa)</t>
+          <t>Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para c</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FN3GPQZM?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M28" s="14"/>
@@ -9644,11 +9384,11 @@
       <c r="AB28"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="19">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="AE28" s="15"/>
       <c r="AF28" s="21">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -9700,7 +9440,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
+          <t>B0G4RSJQVT</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9713,23 +9453,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanent</t>
+          <t>Lubluelu Aspirador de ácaros 3 en 1 para colchones, 18 KPa fuerte potencia de succión, limpiador de colchones contra ácaros,</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FVS559GZ?psc=1</t>
+          <t>https://www.amazon.es/dp/B0G4RSJQVT?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
+          <t>B0G4RSJQVT</t>
         </is>
       </c>
       <c r="M29" s="14"/>
@@ -9750,11 +9490,11 @@
       <c r="AB29"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="19">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE29" s="15"/>
       <c r="AF29" s="21">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -9806,7 +9546,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GBX6FZG4</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9819,23 +9559,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para c</t>
+          <t>Teant Aspirador de ácaros para colchones con luz UV, 16 kPa con pantalla LED, 65 ℃ aire caliente y HEPA, ultrasónico, aromate</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GBX6FZG4?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71TSFHQeA7L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GBX6FZG4</t>
         </is>
       </c>
       <c r="M30" s="14"/>
@@ -9856,11 +9596,11 @@
       <c r="AB30"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="19">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="AE30" s="15"/>
       <c r="AF30" s="21">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -9912,7 +9652,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9925,23 +9665,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirador de ácaros 3 en 1 para colchones, 18 KPa fuerte potencia de succión, limpiador de colchones contra ácaros,</t>
+          <t>Aspiradora De Acaros, Aspiradora Antiacaros con Triple Filtración Y Filtro Lavable, Vibración De Alta Frecuencia, Maquina Ant</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0G4RSJQVT?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GYS43G8G?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="M31" s="14"/>
@@ -9962,11 +9702,11 @@
       <c r="AB31"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="19">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="AE31" s="15"/>
       <c r="AF31" s="21">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -10018,7 +9758,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GBX6FZG4</t>
+          <t>B0H712ZM35</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -10031,23 +9771,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Teant Aspirador de ácaros para colchones con luz UV, 16 kPa con pantalla LED, 65 ℃ aire caliente y HEPA, ultrasónico, aromate</t>
+          <t>Resmafn 15KPa Aspiradora Antiacaros Colchones con Luz UV y Cable 5MsAspirador Ácaros Vibración Depósito Extraíble 1L, 60°C</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GBX6FZG4?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H712ZM35?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71TSFHQeA7L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71KXc8Ab7cL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GBX6FZG4</t>
+          <t>B0H712ZM35</t>
         </is>
       </c>
       <c r="M32" s="14"/>
@@ -10068,11 +9808,11 @@
       <c r="AB32"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="19">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AE32" s="15"/>
       <c r="AF32" s="21">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
@@ -10124,7 +9864,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -10137,23 +9877,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Aspiradora De Acaros, Aspiradora Antiacaros con Triple Filtración Y Filtro Lavable, Vibración De Alta Frecuencia, Maquina Ant</t>
+          <t>Aspirador de colchón recargable inalámbrico portátil para camas sofássAspirador de mano silencioso, limpiador profundo inte</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GYS43G8G?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="M33" s="14"/>
@@ -10173,13 +9913,9 @@
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="2"/>
-      <c r="AD33" s="19">
-        <v>2</v>
-      </c>
+      <c r="AD33" s="19"/>
       <c r="AE33" s="15"/>
-      <c r="AF33" s="21">
-        <v>1</v>
-      </c>
+      <c r="AF33" s="21"/>
       <c r="AG33" s="22">
         <v>0</v>
       </c>
@@ -10230,7 +9966,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0H712ZM35</t>
+          <t>B0HBMBNXJ1</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -10243,23 +9979,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Resmafn 15KPa Aspiradora Antiacaros Colchones con Luz UV y Cable 5MsAspirador Ácaros Vibración Depósito Extraíble 1L, 60°C</t>
+          <t>Aspirador de ácaros para colchón, recargable, con luz UVsAspiradora inalámbrica antiácaros con filtro HEPA y depósito de su</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H712ZM35?psc=1</t>
+          <t>https://www.amazon.es/dp/B0HBMBNXJ1?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71KXc8Ab7cL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61yv1n+ai8L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0H712ZM35</t>
+          <t>B0HBMBNXJ1</t>
         </is>
       </c>
       <c r="M34" s="14"/>
@@ -10279,13 +10015,9 @@
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34" s="2"/>
-      <c r="AD34" s="19">
-        <v>18</v>
-      </c>
+      <c r="AD34" s="19"/>
       <c r="AE34" s="15"/>
-      <c r="AF34" s="21">
-        <v>4.9</v>
-      </c>
+      <c r="AF34" s="21"/>
       <c r="AG34" s="22">
         <v>0</v>
       </c>
@@ -10328,210 +10060,6 @@
       <c r="BP34" s="23"/>
       <c r="BQ34" s="23"/>
       <c r="BR34" s="13"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13">
-        <v>34</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>B0H8Z6R4ZK</t>
-        </is>
-      </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.esundefined</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>Aspirador de colchón recargable inalámbrico portátil para camas sofássAspirador de mano silencioso, limpiador profundo inte</t>
-        </is>
-      </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1</t>
-        </is>
-      </c>
-      <c r="K35" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L35" s="14" t="inlineStr">
-        <is>
-          <t>B0H8Z6R4ZK</t>
-        </is>
-      </c>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="15"/>
-      <c r="U35" s="16"/>
-      <c r="V35" s="15"/>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
-      <c r="Y35" s="19"/>
-      <c r="Z35" s="20"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35" s="2"/>
-      <c r="AD35" s="19"/>
-      <c r="AE35" s="15"/>
-      <c r="AF35" s="21"/>
-      <c r="AG35" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="20"/>
-      <c r="AI35" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ35"/>
-      <c r="AK35" s="13"/>
-      <c r="AL35" s="19"/>
-      <c r="AM35" s="13"/>
-      <c r="AN35" s="13"/>
-      <c r="AO35" s="13"/>
-      <c r="AP35"/>
-      <c r="AQ35" s="19"/>
-      <c r="AR35" s="19"/>
-      <c r="AS35" s="14"/>
-      <c r="AT35" s="13"/>
-      <c r="AU35" s="13"/>
-      <c r="AV35" s="14"/>
-      <c r="AW35" s="13"/>
-      <c r="AX35" s="13"/>
-      <c r="AY35" s="13"/>
-      <c r="AZ35" s="13"/>
-      <c r="BA35" s="13"/>
-      <c r="BB35" s="13"/>
-      <c r="BC35" s="13"/>
-      <c r="BD35" s="13"/>
-      <c r="BE35" s="13"/>
-      <c r="BF35" s="13"/>
-      <c r="BG35" s="13"/>
-      <c r="BH35" s="14"/>
-      <c r="BI35" s="23"/>
-      <c r="BJ35" s="23"/>
-      <c r="BK35" s="23"/>
-      <c r="BL35" s="23"/>
-      <c r="BM35" s="23"/>
-      <c r="BN35" s="23"/>
-      <c r="BO35" s="23"/>
-      <c r="BP35" s="23"/>
-      <c r="BQ35" s="23"/>
-      <c r="BR35" s="13"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13">
-        <v>35</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>B0HBMBNXJ1</t>
-        </is>
-      </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.esundefined</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>Aspirador de ácaros para colchón, recargable, con luz UVsAspiradora inalámbrica antiácaros con filtro HEPA y depósito de su</t>
-        </is>
-      </c>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0HBMBNXJ1?psc=1</t>
-        </is>
-      </c>
-      <c r="K36" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61yv1n+ai8L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L36" s="14" t="inlineStr">
-        <is>
-          <t>B0HBMBNXJ1</t>
-        </is>
-      </c>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="15"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
-      <c r="Y36" s="19"/>
-      <c r="Z36" s="20"/>
-      <c r="AA36"/>
-      <c r="AB36"/>
-      <c r="AC36" s="2"/>
-      <c r="AD36" s="19"/>
-      <c r="AE36" s="15"/>
-      <c r="AF36" s="21"/>
-      <c r="AG36" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="20"/>
-      <c r="AI36" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ36"/>
-      <c r="AK36" s="13"/>
-      <c r="AL36" s="19"/>
-      <c r="AM36" s="13"/>
-      <c r="AN36" s="13"/>
-      <c r="AO36" s="13"/>
-      <c r="AP36"/>
-      <c r="AQ36" s="19"/>
-      <c r="AR36" s="19"/>
-      <c r="AS36" s="14"/>
-      <c r="AT36" s="13"/>
-      <c r="AU36" s="13"/>
-      <c r="AV36" s="14"/>
-      <c r="AW36" s="13"/>
-      <c r="AX36" s="13"/>
-      <c r="AY36" s="13"/>
-      <c r="AZ36" s="13"/>
-      <c r="BA36" s="13"/>
-      <c r="BB36" s="13"/>
-      <c r="BC36" s="13"/>
-      <c r="BD36" s="13"/>
-      <c r="BE36" s="13"/>
-      <c r="BF36" s="13"/>
-      <c r="BG36" s="13"/>
-      <c r="BH36" s="14"/>
-      <c r="BI36" s="23"/>
-      <c r="BJ36" s="23"/>
-      <c r="BK36" s="23"/>
-      <c r="BL36" s="23"/>
-      <c r="BM36" s="23"/>
-      <c r="BN36" s="23"/>
-      <c r="BO36" s="23"/>
-      <c r="BP36" s="23"/>
-      <c r="BQ36" s="23"/>
-      <c r="BR36" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10606,162 +10134,146 @@
     <hyperlink ref="M10" r:id="rId67" tooltip="https://www.amazon.es/b?node=13713592031"/>
     <hyperlink ref="N10" r:id="rId68"/>
     <hyperlink ref="AW10" r:id="rId69" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ASTEKNQOF9QUQ"/>
-    <hyperlink ref="C11" r:id="rId70" tooltip="https://www.amazon.es/dp/B0F2MQCLRJ"/>
-    <hyperlink ref="G11" r:id="rId71" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=CREATULIZE"/>
-    <hyperlink ref="J11" r:id="rId72" tooltip="https://www.amazon.es/dp/B0F2MQCLRJ?psc=1"/>
-    <hyperlink ref="K11" r:id="rId73" tooltip="https://m.media-amazon.com/images/I/313+mKfH96L._AC_US600_.jpg"/>
-    <hyperlink ref="L11" r:id="rId74" tooltip="https://www.amazon.es/dp/B0F2MQCLRJ"/>
-    <hyperlink ref="M11" r:id="rId75" tooltip="https://www.amazon.es/b?node=2404713031"/>
+    <hyperlink ref="C11" r:id="rId70" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
+    <hyperlink ref="G11" r:id="rId71" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J11" r:id="rId72" tooltip="https://www.amazon.es/dp/B0GF7CNTYL?psc=1"/>
+    <hyperlink ref="K11" r:id="rId73" tooltip="https://m.media-amazon.com/images/I/41CQc-U9WtL._AC_US600_.jpg"/>
+    <hyperlink ref="L11" r:id="rId74" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
+    <hyperlink ref="M11" r:id="rId75" tooltip="https://www.amazon.es/b?node=13713592031"/>
     <hyperlink ref="N11" r:id="rId76"/>
-    <hyperlink ref="AW11" r:id="rId77" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AWR1VM0K04YAS"/>
-    <hyperlink ref="C12" r:id="rId78" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
-    <hyperlink ref="G12" r:id="rId79" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
-    <hyperlink ref="J12" r:id="rId80" tooltip="https://www.amazon.es/dp/B0GF7CNTYL?psc=1"/>
-    <hyperlink ref="K12" r:id="rId81" tooltip="https://m.media-amazon.com/images/I/41CQc-U9WtL._AC_US600_.jpg"/>
-    <hyperlink ref="L12" r:id="rId82" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
+    <hyperlink ref="AW11" r:id="rId77" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
+    <hyperlink ref="C12" r:id="rId78" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1"/>
+    <hyperlink ref="G12" r:id="rId79" tooltip="https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0CJFR8YZ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J12" r:id="rId80" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1?psc=1"/>
+    <hyperlink ref="K12" r:id="rId81" tooltip="https://images-na.ssl-images-amazon.com/images/I/71wwrAJ4EpL._AC_US600_.jpg"/>
+    <hyperlink ref="L12" r:id="rId82" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1"/>
     <hyperlink ref="M12" r:id="rId83" tooltip="https://www.amazon.es/b?node=13713592031"/>
     <hyperlink ref="N12" r:id="rId84"/>
-    <hyperlink ref="AW12" r:id="rId85" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
-    <hyperlink ref="C13" r:id="rId86" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1"/>
-    <hyperlink ref="G13" r:id="rId87" tooltip="https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0CJFR8YZ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J13" r:id="rId88" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1?psc=1"/>
-    <hyperlink ref="K13" r:id="rId89" tooltip="https://images-na.ssl-images-amazon.com/images/I/71wwrAJ4EpL._AC_US600_.jpg"/>
-    <hyperlink ref="L13" r:id="rId90" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1"/>
-    <hyperlink ref="M13" r:id="rId91" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N13" r:id="rId92"/>
-    <hyperlink ref="AW13" r:id="rId93" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SBFZKR4LHBTM"/>
-    <hyperlink ref="C14" r:id="rId94" tooltip="https://www.amazon.es/dp/B0D83SRY9V"/>
-    <hyperlink ref="G14" r:id="rId95" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J14" r:id="rId96" tooltip="https://www.amazon.es/dp/B0D83SRY9V?psc=1"/>
-    <hyperlink ref="K14" r:id="rId97" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51LjSaAmb9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId98" tooltip="https://www.amazon.es/dp/B0D83SRY9V"/>
-    <hyperlink ref="C15" r:id="rId99" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ"/>
-    <hyperlink ref="G15" r:id="rId100" tooltip="https://www.amazon.es/Jimmy/b/ref=bl_dp_s_web_17484947031?ie=UTF8&amp;node=17484947031&amp;field-lbr_brands_browse-bin=Jimmy"/>
-    <hyperlink ref="J15" r:id="rId101" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ?psc=1"/>
-    <hyperlink ref="K15" r:id="rId102" tooltip="https://m.media-amazon.com/images/I/41BwZxWS8oL._AC_US600_.jpg"/>
-    <hyperlink ref="L15" r:id="rId103" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ"/>
-    <hyperlink ref="M15" r:id="rId104" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N15" r:id="rId105"/>
-    <hyperlink ref="AW15" r:id="rId106" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UUYGTGLOQBB0"/>
-    <hyperlink ref="C16" r:id="rId107" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL"/>
-    <hyperlink ref="G16" r:id="rId108" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J16" r:id="rId109" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL?psc=1"/>
-    <hyperlink ref="K16" r:id="rId110" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71X5KPbPpoL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId111" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL"/>
-    <hyperlink ref="C17" r:id="rId112" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX"/>
-    <hyperlink ref="G17" r:id="rId113" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J17" r:id="rId114" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX?psc=1"/>
-    <hyperlink ref="K17" r:id="rId115" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61YjHSHoT6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId116" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX"/>
-    <hyperlink ref="C18" r:id="rId117" tooltip="https://www.amazon.es/dp/B0DT1D15C6"/>
-    <hyperlink ref="G18" r:id="rId118" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J18" r:id="rId119" tooltip="https://www.amazon.es/dp/B0DT1D15C6?psc=1"/>
-    <hyperlink ref="K18" r:id="rId120" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81vdWh-NSLL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId121" tooltip="https://www.amazon.es/dp/B0DT1D15C6"/>
-    <hyperlink ref="C19" r:id="rId122" tooltip="https://www.amazon.es/dp/B0DWK8LJF9"/>
-    <hyperlink ref="G19" r:id="rId123" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J19" r:id="rId124" tooltip="https://www.amazon.es/dp/B0DWK8LJF9?psc=1"/>
-    <hyperlink ref="K19" r:id="rId125" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61TZ0rMGBrL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId126" tooltip="https://www.amazon.es/dp/B0DWK8LJF9"/>
-    <hyperlink ref="C20" r:id="rId127" tooltip="https://www.amazon.es/dp/B0F6XNKG8M"/>
-    <hyperlink ref="G20" r:id="rId128" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J20" r:id="rId129" tooltip="https://www.amazon.es/dp/B0F6XNKG8M?psc=1"/>
-    <hyperlink ref="K20" r:id="rId130" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId131" tooltip="https://www.amazon.es/dp/B0F6XNKG8M"/>
-    <hyperlink ref="C21" r:id="rId132" tooltip="https://www.amazon.es/dp/B0F8HD3649"/>
-    <hyperlink ref="G21" r:id="rId133" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J21" r:id="rId134" tooltip="https://www.amazon.es/dp/B0F8HD3649?psc=1"/>
-    <hyperlink ref="K21" r:id="rId135" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId136" tooltip="https://www.amazon.es/dp/B0F8HD3649"/>
-    <hyperlink ref="C22" r:id="rId137" tooltip="https://www.amazon.es/dp/B0F9NJM4V9"/>
-    <hyperlink ref="G22" r:id="rId138" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J22" r:id="rId139" tooltip="https://www.amazon.es/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K22" r:id="rId140" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId141" tooltip="https://www.amazon.es/dp/B0F9NJM4V9"/>
-    <hyperlink ref="C23" r:id="rId142" tooltip="https://www.amazon.es/dp/B0FBGQY9YP"/>
-    <hyperlink ref="G23" r:id="rId143" tooltip="https://www.amazon.es/stores/Fey/page/43F7FFA5-3E54-4A0B-BF57-3795C4422856?lp_asin=B0FBGQY9YP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J23" r:id="rId144" tooltip="https://www.amazon.es/dp/B0FBGQY9YP?psc=1"/>
-    <hyperlink ref="K23" r:id="rId145" tooltip="https://images-na.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_US600_.jpg"/>
-    <hyperlink ref="L23" r:id="rId146" tooltip="https://www.amazon.es/dp/B0FBGQY9YP"/>
-    <hyperlink ref="M23" r:id="rId147" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N23" r:id="rId148"/>
-    <hyperlink ref="AW23" r:id="rId149" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3MSJ66TMU8M67"/>
-    <hyperlink ref="C24" r:id="rId150" tooltip="https://www.amazon.es/dp/B0FBX24WH6"/>
-    <hyperlink ref="G24" r:id="rId151" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=syayw"/>
-    <hyperlink ref="J24" r:id="rId152" tooltip="https://www.amazon.es/dp/B0FBX24WH6?psc=1"/>
-    <hyperlink ref="K24" r:id="rId153" tooltip="https://images-na.ssl-images-amazon.com/images/I/61LvanTuKlL._AC_US600_.jpg"/>
-    <hyperlink ref="L24" r:id="rId154" tooltip="https://www.amazon.es/dp/B0FBX24WH6"/>
-    <hyperlink ref="M24" r:id="rId155" tooltip="https://www.amazon.es/b?node=2404713031"/>
-    <hyperlink ref="N24" r:id="rId156"/>
-    <hyperlink ref="AW24" r:id="rId157" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3T9BSXCSWI46M"/>
-    <hyperlink ref="C25" r:id="rId158" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
-    <hyperlink ref="G25" r:id="rId159" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J25" r:id="rId160" tooltip="https://www.amazon.es/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K25" r:id="rId161" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId162" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
-    <hyperlink ref="C26" r:id="rId163" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
-    <hyperlink ref="G26" r:id="rId164" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J26" r:id="rId165" tooltip="https://www.amazon.es/dp/B0FKRC3KQY?psc=1"/>
-    <hyperlink ref="K26" r:id="rId166" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId167" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
-    <hyperlink ref="C27" r:id="rId168" tooltip="https://www.amazon.es/dp/B0FLXSG7JN"/>
-    <hyperlink ref="G27" r:id="rId169" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J27" r:id="rId170" tooltip="https://www.amazon.es/dp/B0FLXSG7JN?psc=1"/>
-    <hyperlink ref="K27" r:id="rId171" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId172" tooltip="https://www.amazon.es/dp/B0FLXSG7JN"/>
-    <hyperlink ref="C28" r:id="rId173" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
-    <hyperlink ref="G28" r:id="rId174" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J28" r:id="rId175" tooltip="https://www.amazon.es/dp/B0FN3GPQZM?psc=1"/>
-    <hyperlink ref="K28" r:id="rId176" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId177" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
-    <hyperlink ref="C29" r:id="rId178" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
-    <hyperlink ref="G29" r:id="rId179" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J29" r:id="rId180" tooltip="https://www.amazon.es/dp/B0FVS559GZ?psc=1"/>
-    <hyperlink ref="K29" r:id="rId181" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId182" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
-    <hyperlink ref="C30" r:id="rId183" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
-    <hyperlink ref="G30" r:id="rId184" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J30" r:id="rId185" tooltip="https://www.amazon.es/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K30" r:id="rId186" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId187" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
-    <hyperlink ref="C31" r:id="rId188" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
-    <hyperlink ref="G31" r:id="rId189" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J31" r:id="rId190" tooltip="https://www.amazon.es/dp/B0G4RSJQVT?psc=1"/>
-    <hyperlink ref="K31" r:id="rId191" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId192" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
-    <hyperlink ref="C32" r:id="rId193" tooltip="https://www.amazon.es/dp/B0GBX6FZG4"/>
-    <hyperlink ref="G32" r:id="rId194" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J32" r:id="rId195" tooltip="https://www.amazon.es/dp/B0GBX6FZG4?psc=1"/>
-    <hyperlink ref="K32" r:id="rId196" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TSFHQeA7L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId197" tooltip="https://www.amazon.es/dp/B0GBX6FZG4"/>
-    <hyperlink ref="C33" r:id="rId198" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
-    <hyperlink ref="G33" r:id="rId199" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J33" r:id="rId200" tooltip="https://www.amazon.es/dp/B0GYS43G8G?psc=1"/>
-    <hyperlink ref="K33" r:id="rId201" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId202" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
-    <hyperlink ref="C34" r:id="rId203" tooltip="https://www.amazon.es/dp/B0H712ZM35"/>
-    <hyperlink ref="G34" r:id="rId204" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J34" r:id="rId205" tooltip="https://www.amazon.es/dp/B0H712ZM35?psc=1"/>
-    <hyperlink ref="K34" r:id="rId206" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71KXc8Ab7cL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId207" tooltip="https://www.amazon.es/dp/B0H712ZM35"/>
-    <hyperlink ref="C35" r:id="rId208" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="G35" r:id="rId209" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J35" r:id="rId210" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1"/>
-    <hyperlink ref="K35" r:id="rId211" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId212" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="C36" r:id="rId213" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1"/>
-    <hyperlink ref="G36" r:id="rId214" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J36" r:id="rId215" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1?psc=1"/>
-    <hyperlink ref="K36" r:id="rId216" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61yv1n+ai8L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId217" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1"/>
+    <hyperlink ref="AW12" r:id="rId85" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SBFZKR4LHBTM"/>
+    <hyperlink ref="C13" r:id="rId86" tooltip="https://www.amazon.es/dp/B0D83SRY9V"/>
+    <hyperlink ref="G13" r:id="rId87" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J13" r:id="rId88" tooltip="https://www.amazon.es/dp/B0D83SRY9V?psc=1"/>
+    <hyperlink ref="K13" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51LjSaAmb9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId90" tooltip="https://www.amazon.es/dp/B0D83SRY9V"/>
+    <hyperlink ref="C14" r:id="rId91" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ"/>
+    <hyperlink ref="G14" r:id="rId92" tooltip="https://www.amazon.es/Jimmy/b/ref=bl_dp_s_web_17484947031?ie=UTF8&amp;node=17484947031&amp;field-lbr_brands_browse-bin=Jimmy"/>
+    <hyperlink ref="J14" r:id="rId93" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ?psc=1"/>
+    <hyperlink ref="K14" r:id="rId94" tooltip="https://m.media-amazon.com/images/I/41BwZxWS8oL._AC_US600_.jpg"/>
+    <hyperlink ref="L14" r:id="rId95" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ"/>
+    <hyperlink ref="M14" r:id="rId96" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N14" r:id="rId97"/>
+    <hyperlink ref="AW14" r:id="rId98" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UUYGTGLOQBB0"/>
+    <hyperlink ref="C15" r:id="rId99" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL"/>
+    <hyperlink ref="G15" r:id="rId100" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J15" r:id="rId101" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL?psc=1"/>
+    <hyperlink ref="K15" r:id="rId102" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71X5KPbPpoL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId103" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL"/>
+    <hyperlink ref="C16" r:id="rId104" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX"/>
+    <hyperlink ref="G16" r:id="rId105" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J16" r:id="rId106" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX?psc=1"/>
+    <hyperlink ref="K16" r:id="rId107" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61YjHSHoT6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId108" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX"/>
+    <hyperlink ref="C17" r:id="rId109" tooltip="https://www.amazon.es/dp/B0DT1D15C6"/>
+    <hyperlink ref="G17" r:id="rId110" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J17" r:id="rId111" tooltip="https://www.amazon.es/dp/B0DT1D15C6?psc=1"/>
+    <hyperlink ref="K17" r:id="rId112" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81vdWh-NSLL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId113" tooltip="https://www.amazon.es/dp/B0DT1D15C6"/>
+    <hyperlink ref="C18" r:id="rId114" tooltip="https://www.amazon.es/dp/B0DWK8LJF9"/>
+    <hyperlink ref="G18" r:id="rId115" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J18" r:id="rId116" tooltip="https://www.amazon.es/dp/B0DWK8LJF9?psc=1"/>
+    <hyperlink ref="K18" r:id="rId117" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61TZ0rMGBrL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId118" tooltip="https://www.amazon.es/dp/B0DWK8LJF9"/>
+    <hyperlink ref="C19" r:id="rId119" tooltip="https://www.amazon.es/dp/B0F6XNKG8M"/>
+    <hyperlink ref="G19" r:id="rId120" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J19" r:id="rId121" tooltip="https://www.amazon.es/dp/B0F6XNKG8M?psc=1"/>
+    <hyperlink ref="K19" r:id="rId122" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId123" tooltip="https://www.amazon.es/dp/B0F6XNKG8M"/>
+    <hyperlink ref="C20" r:id="rId124" tooltip="https://www.amazon.es/dp/B0F8HD3649"/>
+    <hyperlink ref="G20" r:id="rId125" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J20" r:id="rId126" tooltip="https://www.amazon.es/dp/B0F8HD3649?psc=1"/>
+    <hyperlink ref="K20" r:id="rId127" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId128" tooltip="https://www.amazon.es/dp/B0F8HD3649"/>
+    <hyperlink ref="C21" r:id="rId129" tooltip="https://www.amazon.es/dp/B0F9NJM4V9"/>
+    <hyperlink ref="G21" r:id="rId130" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J21" r:id="rId131" tooltip="https://www.amazon.es/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K21" r:id="rId132" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId133" tooltip="https://www.amazon.es/dp/B0F9NJM4V9"/>
+    <hyperlink ref="C22" r:id="rId134" tooltip="https://www.amazon.es/dp/B0FBGQY9YP"/>
+    <hyperlink ref="G22" r:id="rId135" tooltip="https://www.amazon.es/stores/Fey/page/43F7FFA5-3E54-4A0B-BF57-3795C4422856?lp_asin=B0FBGQY9YP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J22" r:id="rId136" tooltip="https://www.amazon.es/dp/B0FBGQY9YP?psc=1"/>
+    <hyperlink ref="K22" r:id="rId137" tooltip="https://images-na.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_US600_.jpg"/>
+    <hyperlink ref="L22" r:id="rId138" tooltip="https://www.amazon.es/dp/B0FBGQY9YP"/>
+    <hyperlink ref="M22" r:id="rId139" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N22" r:id="rId140"/>
+    <hyperlink ref="AW22" r:id="rId141" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3MSJ66TMU8M67"/>
+    <hyperlink ref="C23" r:id="rId142" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
+    <hyperlink ref="G23" r:id="rId143" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J23" r:id="rId144" tooltip="https://www.amazon.es/dp/B0FDWVV95V?psc=1"/>
+    <hyperlink ref="K23" r:id="rId145" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId146" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
+    <hyperlink ref="C24" r:id="rId147" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
+    <hyperlink ref="G24" r:id="rId148" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J24" r:id="rId149" tooltip="https://www.amazon.es/dp/B0FKRC3KQY?psc=1"/>
+    <hyperlink ref="K24" r:id="rId150" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId151" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
+    <hyperlink ref="C25" r:id="rId152" tooltip="https://www.amazon.es/dp/B0FLXSG7JN"/>
+    <hyperlink ref="G25" r:id="rId153" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J25" r:id="rId154" tooltip="https://www.amazon.es/dp/B0FLXSG7JN?psc=1"/>
+    <hyperlink ref="K25" r:id="rId155" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId156" tooltip="https://www.amazon.es/dp/B0FLXSG7JN"/>
+    <hyperlink ref="C26" r:id="rId157" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
+    <hyperlink ref="G26" r:id="rId158" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J26" r:id="rId159" tooltip="https://www.amazon.es/dp/B0FN3GPQZM?psc=1"/>
+    <hyperlink ref="K26" r:id="rId160" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId161" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
+    <hyperlink ref="C27" r:id="rId162" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
+    <hyperlink ref="G27" r:id="rId163" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J27" r:id="rId164" tooltip="https://www.amazon.es/dp/B0FVS559GZ?psc=1"/>
+    <hyperlink ref="K27" r:id="rId165" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId166" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
+    <hyperlink ref="C28" r:id="rId167" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
+    <hyperlink ref="G28" r:id="rId168" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J28" r:id="rId169" tooltip="https://www.amazon.es/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K28" r:id="rId170" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId171" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
+    <hyperlink ref="C29" r:id="rId172" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
+    <hyperlink ref="G29" r:id="rId173" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J29" r:id="rId174" tooltip="https://www.amazon.es/dp/B0G4RSJQVT?psc=1"/>
+    <hyperlink ref="K29" r:id="rId175" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId176" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
+    <hyperlink ref="C30" r:id="rId177" tooltip="https://www.amazon.es/dp/B0GBX6FZG4"/>
+    <hyperlink ref="G30" r:id="rId178" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J30" r:id="rId179" tooltip="https://www.amazon.es/dp/B0GBX6FZG4?psc=1"/>
+    <hyperlink ref="K30" r:id="rId180" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TSFHQeA7L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId181" tooltip="https://www.amazon.es/dp/B0GBX6FZG4"/>
+    <hyperlink ref="C31" r:id="rId182" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
+    <hyperlink ref="G31" r:id="rId183" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J31" r:id="rId184" tooltip="https://www.amazon.es/dp/B0GYS43G8G?psc=1"/>
+    <hyperlink ref="K31" r:id="rId185" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId186" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
+    <hyperlink ref="C32" r:id="rId187" tooltip="https://www.amazon.es/dp/B0H712ZM35"/>
+    <hyperlink ref="G32" r:id="rId188" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J32" r:id="rId189" tooltip="https://www.amazon.es/dp/B0H712ZM35?psc=1"/>
+    <hyperlink ref="K32" r:id="rId190" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71KXc8Ab7cL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId191" tooltip="https://www.amazon.es/dp/B0H712ZM35"/>
+    <hyperlink ref="C33" r:id="rId192" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="G33" r:id="rId193" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J33" r:id="rId194" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1"/>
+    <hyperlink ref="K33" r:id="rId195" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId196" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="C34" r:id="rId197" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1"/>
+    <hyperlink ref="G34" r:id="rId198" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J34" r:id="rId199" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1?psc=1"/>
+    <hyperlink ref="K34" r:id="rId200" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61yv1n+ai8L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId201" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1"/>
   </hyperlinks>
-  <drawing r:id="rId218"/>
+  <drawing r:id="rId202"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -10825,7 +10337,7 @@
         <v>103.6046511627907</v>
       </c>
       <c r="G2" s="22">
-        <v>0.2471264367816092</v>
+        <v>0.25146198830409355</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10846,7 +10358,7 @@
         <v>170.0</v>
       </c>
       <c r="G3" s="22">
-        <v>0.11781609195402298</v>
+        <v>0.11988304093567251</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10867,7 +10379,7 @@
         <v>102.8125</v>
       </c>
       <c r="G4" s="22">
-        <v>0.1839080459770115</v>
+        <v>0.1871345029239766</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10888,7 +10400,7 @@
         <v>80.0</v>
       </c>
       <c r="G5" s="22">
-        <v>0.09482758620689655</v>
+        <v>0.09649122807017543</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10909,7 +10421,7 @@
         <v>64.0</v>
       </c>
       <c r="G6" s="22">
-        <v>0.07183908045977011</v>
+        <v>0.07309941520467836</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10930,7 +10442,7 @@
         <v>70.26315789473684</v>
       </c>
       <c r="G7" s="22">
-        <v>0.05459770114942529</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10951,7 +10463,7 @@
         <v>32.0</v>
       </c>
       <c r="G8" s="22">
-        <v>0.11206896551724138</v>
+        <v>0.11403508771929824</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10972,55 +10484,53 @@
         <v>26.0</v>
       </c>
       <c r="G9" s="22">
-        <v>0.09770114942528736</v>
+        <v>0.09941520467836257</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>CREATULIZE</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="B10" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" s="15">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
       <c r="F10" s="20">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="G10" s="22">
-        <v>0.017241379310344827</v>
+        <v>0.0029239766081871343</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi</t>
+          <t>Fey</t>
         </is>
       </c>
       <c r="B11" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
-      <c r="F11" s="20">
-        <v>25.0</v>
-      </c>
+      <c r="F11" s="20"/>
       <c r="G11" s="22">
-        <v>0.0028735632183908046</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Fey</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B12" s="15">
@@ -11033,44 +10543,6 @@
       <c r="E12" s="15"/>
       <c r="F12" s="20"/>
       <c r="G12" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B13" s="15">
-        <v>0</v>
-      </c>
-      <c r="C13" s="15">
-        <v>0</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>syayw</t>
-        </is>
-      </c>
-      <c r="B14" s="15">
-        <v>0</v>
-      </c>
-      <c r="C14" s="15">
-        <v>0</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="22">
         <v>0.0</v>
       </c>
     </row>
@@ -11082,7 +10554,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -11146,7 +10618,7 @@
         <v>91.31944444444444</v>
       </c>
       <c r="G2" s="22">
-        <v>0.41379310344827586</v>
+        <v>0.42105263157894735</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11167,7 +10639,7 @@
         <v>170.0</v>
       </c>
       <c r="G3" s="22">
-        <v>0.11781609195402298</v>
+        <v>0.11988304093567251</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11188,7 +10660,7 @@
         <v>154.0</v>
       </c>
       <c r="G4" s="22">
-        <v>0.07183908045977011</v>
+        <v>0.07309941520467836</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11209,7 +10681,7 @@
         <v>70.0</v>
       </c>
       <c r="G5" s="22">
-        <v>0.11206896551724138</v>
+        <v>0.11403508771929824</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11230,7 +10702,7 @@
         <v>70.26315789473684</v>
       </c>
       <c r="G6" s="22">
-        <v>0.05459770114942529</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11251,7 +10723,7 @@
         <v>32.0</v>
       </c>
       <c r="G7" s="22">
-        <v>0.11206896551724138</v>
+        <v>0.11403508771929824</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11272,55 +10744,53 @@
         <v>26.0</v>
       </c>
       <c r="G8" s="22">
-        <v>0.09770114942528736</v>
+        <v>0.09941520467836257</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Romiromi</t>
+          <t>liwantech</t>
         </is>
       </c>
       <c r="B9" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9" s="15">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="20">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="G9" s="22">
-        <v>0.017241379310344827</v>
+        <v>0.0029239766081871343</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>liwantech</t>
+          <t>GOOD PRICE ONLY</t>
         </is>
       </c>
       <c r="B10" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
-      <c r="F10" s="20">
-        <v>25.0</v>
-      </c>
+      <c r="F10" s="20"/>
       <c r="G10" s="22">
-        <v>0.0028735632183908046</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>GOOD PRICE ONLY</t>
+          <t>Jierun-EU</t>
         </is>
       </c>
       <c r="B11" s="15">
@@ -11339,7 +10809,7 @@
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Jierun-EU</t>
+          <t>NEXO HOME</t>
         </is>
       </c>
       <c r="B12" s="15">
@@ -11358,7 +10828,7 @@
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>NEXO HOME</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B13" s="15">
@@ -11371,44 +10841,6 @@
       <c r="E13" s="15"/>
       <c r="F13" s="20"/>
       <c r="G13" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B14" s="15">
-        <v>0</v>
-      </c>
-      <c r="C14" s="15">
-        <v>0</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>nousaeg</t>
-        </is>
-      </c>
-      <c r="B15" s="15">
-        <v>0</v>
-      </c>
-      <c r="C15" s="15">
-        <v>0</v>
-      </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="22">
         <v>0.0</v>
       </c>
     </row>
